--- a/artfynd/A 24606-2025 artfynd.xlsx
+++ b/artfynd/A 24606-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>123420610</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -805,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420609</v>
+        <v>123420612</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600268</v>
+        <v>600225</v>
       </c>
       <c r="R3" t="n">
-        <v>6795654</v>
+        <v>6795657</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +874,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2499</t>
+          <t>2024_2496</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -938,12 +928,7 @@
         <v>123420613</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,12 +945,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1068,12 +1053,7 @@
         <v>123420614</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,12 +1070,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1195,47 +1175,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420608</v>
+        <v>123420609</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600269</v>
+        <v>600268</v>
       </c>
       <c r="R6" t="n">
-        <v>6795658</v>
+        <v>6795654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2500</t>
+          <t>2024_2499</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1325,15 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123420615</v>
+        <v>123420611</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600236</v>
+        <v>600227</v>
       </c>
       <c r="R7" t="n">
-        <v>6795741</v>
+        <v>6795654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1374,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2493</t>
+          <t>2024_2497</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,15 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123420612</v>
+        <v>123420615</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,21 +1436,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1504,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600225</v>
+        <v>600236</v>
       </c>
       <c r="R8" t="n">
-        <v>6795657</v>
+        <v>6795741</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,7 +1499,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_2496</t>
+          <t>2024_2493</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1544,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1554,7 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1585,47 +1550,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123420611</v>
+        <v>123420608</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1634,10 +1594,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600227</v>
+        <v>600269</v>
       </c>
       <c r="R9" t="n">
-        <v>6795654</v>
+        <v>6795658</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1664,7 +1624,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_2497</t>
+          <t>2024_2500</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1674,7 +1634,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1644,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 24606-2025 artfynd.xlsx
+++ b/artfynd/A 24606-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420610</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420612</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420613</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1172,6 +1192,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420614</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1297,6 +1322,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420609</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1422,6 +1452,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420611</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1547,6 +1582,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420615</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1672,8 +1712,23 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420608</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>